--- a/output/roomself_excel/918.xlsx
+++ b/output/roomself_excel/918.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>94600</v>
+        <v>108240</v>
       </c>
       <c r="D2" t="n">
-        <v>2600</v>
+        <v>2632</v>
       </c>
       <c r="E2" t="n">
-        <v>449</v>
+        <v>352</v>
       </c>
       <c r="F2" t="n">
-        <v>258</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>236715</v>
+        <v>134867</v>
       </c>
       <c r="D3" t="n">
-        <v>5732</v>
+        <v>3020</v>
       </c>
       <c r="E3" t="n">
-        <v>794</v>
+        <v>444</v>
       </c>
       <c r="F3" t="n">
-        <v>702</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8755</v>
+        <v>94600</v>
       </c>
       <c r="D4" t="n">
-        <v>752</v>
+        <v>2600</v>
       </c>
       <c r="E4" t="n">
-        <v>125</v>
+        <v>449</v>
       </c>
       <c r="F4" t="n">
-        <v>107</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67575</v>
+        <v>101395</v>
       </c>
       <c r="D6" t="n">
-        <v>3028</v>
+        <v>2684</v>
       </c>
       <c r="E6" t="n">
-        <v>704</v>
+        <v>329</v>
       </c>
       <c r="F6" t="n">
-        <v>265</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>101395</v>
+        <v>37080</v>
       </c>
       <c r="D7" t="n">
-        <v>2684</v>
+        <v>1544</v>
       </c>
       <c r="E7" t="n">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>108240</v>
+        <v>14229</v>
       </c>
       <c r="D8" t="n">
-        <v>2632</v>
+        <v>984</v>
       </c>
       <c r="E8" t="n">
-        <v>352</v>
+        <v>93</v>
       </c>
       <c r="F8" t="n">
-        <v>347</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11742</v>
+        <v>101848</v>
       </c>
       <c r="D9" t="n">
-        <v>868</v>
+        <v>3476</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>334</v>
       </c>
       <c r="F9" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37080</v>
+        <v>14973</v>
       </c>
       <c r="D10" t="n">
-        <v>1544</v>
+        <v>1016</v>
       </c>
       <c r="E10" t="n">
-        <v>341</v>
+        <v>108</v>
       </c>
       <c r="F10" t="n">
-        <v>202</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28428</v>
+        <v>8755</v>
       </c>
       <c r="D11" t="n">
-        <v>1376</v>
+        <v>752</v>
       </c>
       <c r="E11" t="n">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="F11" t="n">
-        <v>22</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14229</v>
+        <v>11742</v>
       </c>
       <c r="D12" t="n">
-        <v>984</v>
+        <v>868</v>
       </c>
       <c r="E12" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="F12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14973</v>
+        <v>25920</v>
       </c>
       <c r="D13" t="n">
-        <v>1016</v>
+        <v>1344</v>
       </c>
       <c r="E13" t="n">
-        <v>108</v>
+        <v>236</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25920</v>
+        <v>67575</v>
       </c>
       <c r="D14" t="n">
-        <v>1344</v>
+        <v>3028</v>
       </c>
       <c r="E14" t="n">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="F14" t="n">
-        <v>120</v>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>28428</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1376</v>
+      </c>
+      <c r="E15" t="n">
+        <v>138</v>
+      </c>
+      <c r="F15" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/918.xlsx
+++ b/output/roomself_excel/918.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2632</v>
       </c>
-      <c r="E2" t="n">
-        <v>352</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>347</v>
+        <v>330</v>
+      </c>
+      <c r="G2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>328</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>3020</v>
       </c>
-      <c r="E3" t="n">
-        <v>444</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>343</v>
+        <v>425</v>
+      </c>
+      <c r="G3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>322</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>2600</v>
       </c>
-      <c r="E4" t="n">
-        <v>449</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>258</v>
+        <v>220</v>
+      </c>
+      <c r="G4" t="n">
+        <v>19</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>625</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +609,27 @@
       <c r="D5" t="n">
         <v>2744</v>
       </c>
-      <c r="E5" t="n">
-        <v>446</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>135</v>
+        <v>329</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>357</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -563,10 +647,26 @@
       <c r="D6" t="n">
         <v>2684</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>293</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>329</v>
       </c>
-      <c r="F6" t="n">
+      <c r="J6" t="n">
         <v>22</v>
       </c>
     </row>
@@ -585,11 +685,27 @@
       <c r="D7" t="n">
         <v>1544</v>
       </c>
-      <c r="E7" t="n">
-        <v>341</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>202</v>
+        <v>206</v>
+      </c>
+      <c r="G7" t="n">
+        <v>22</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>180</v>
+      </c>
+      <c r="J7" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +723,20 @@
       <c r="D8" t="n">
         <v>984</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>93</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>19</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +753,20 @@
       <c r="D9" t="n">
         <v>3476</v>
       </c>
-      <c r="E9" t="n">
-        <v>334</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
+        <v>323</v>
+      </c>
+      <c r="G9" t="n">
         <v>19</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +783,20 @@
       <c r="D10" t="n">
         <v>1016</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>108</v>
       </c>
-      <c r="F10" t="n">
-        <v>22</v>
-      </c>
+      <c r="G10" t="n">
+        <v>22</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,11 +813,27 @@
       <c r="D11" t="n">
         <v>752</v>
       </c>
-      <c r="E11" t="n">
-        <v>125</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>107</v>
+        <v>85</v>
+      </c>
+      <c r="G11" t="n">
+        <v>22</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>103</v>
+      </c>
+      <c r="J11" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -695,12 +851,20 @@
       <c r="D12" t="n">
         <v>868</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>103</v>
       </c>
-      <c r="F12" t="n">
-        <v>22</v>
-      </c>
+      <c r="G12" t="n">
+        <v>22</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,11 +881,27 @@
       <c r="D13" t="n">
         <v>1344</v>
       </c>
-      <c r="E13" t="n">
-        <v>236</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>120</v>
+        <v>240</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>216</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -739,11 +919,27 @@
       <c r="D14" t="n">
         <v>3028</v>
       </c>
-      <c r="E14" t="n">
-        <v>265</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>218</v>
+        <v>196</v>
+      </c>
+      <c r="G14" t="n">
+        <v>22</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>221</v>
+      </c>
+      <c r="J14" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -761,12 +957,20 @@
       <c r="D15" t="n">
         <v>1376</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>138</v>
       </c>
-      <c r="F15" t="n">
-        <v>22</v>
-      </c>
+      <c r="G15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
